--- a/Friopacking_Objetivos_2_3_4_5.xlsx
+++ b/Friopacking_Objetivos_2_3_4_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrodriguez\Desktop\Directorio J\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86072B46-B602-4DAD-93AB-4801FB1081DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F73501-D9AD-4B24-B256-BB9EA1D7D8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="180">
   <si>
     <t>OBJETIVO 2 — EJECUTAR PROYECTOS CON REFRIGERANTE CO2</t>
   </si>
@@ -592,7 +592,7 @@
     <numFmt numFmtId="165" formatCode="[$$-540A]#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1073,7 +1073,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1236,30 +1236,6 @@
     <xf numFmtId="0" fontId="12" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1319,37 +1295,61 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1630,84 +1630,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
     </row>
     <row r="9" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="42" t="s">
@@ -1939,148 +1939,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -2202,17 +2202,17 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -2476,17 +2476,17 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="58" t="s">
+      <c r="A32" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
@@ -2562,16 +2562,16 @@
       <c r="E36" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="F36" s="90" t="s">
+      <c r="F36" s="75" t="s">
         <v>179</v>
       </c>
       <c r="G36" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="H36" s="91" t="s">
+      <c r="H36" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="I36" s="92" t="s">
+      <c r="I36" s="77" t="s">
         <v>159</v>
       </c>
       <c r="J36" s="45">
@@ -2583,17 +2583,12 @@
       <c r="L36" s="48">
         <v>7</v>
       </c>
-      <c r="M36" s="93">
+      <c r="M36" s="78">
         <v>2026</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B6:I6"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="B7:I7"/>
@@ -2601,6 +2596,11 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B6:I6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I36" xr:uid="{1D3A478F-344B-4E54-B296-768D75F24C9F}">
@@ -2628,65 +2628,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="3" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
     </row>
     <row r="4" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
     </row>
     <row r="5" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
     </row>
     <row r="6" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
     </row>
     <row r="7" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
     </row>
     <row r="9" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="89" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="89"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="91"/>
     </row>
     <row r="10" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
@@ -2757,476 +2757,479 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
     </row>
     <row r="16" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="62" t="s">
+      <c r="D16" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="64" t="s">
+      <c r="F16" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="56" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="58">
         <v>3500000</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="69" t="s">
+      <c r="E17" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="70" t="s">
+      <c r="G17" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="66">
+      <c r="C18" s="58">
         <v>3000000</v>
       </c>
-      <c r="D18" s="67" t="s">
+      <c r="D18" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F18" s="70" t="s">
+      <c r="F18" s="62" t="s">
         <v>160</v>
       </c>
-      <c r="G18" s="70" t="s">
+      <c r="G18" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="66">
+      <c r="C19" s="58">
         <v>1950000</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="66">
+      <c r="C20" s="58">
         <v>1572931.74</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="74" t="s">
+      <c r="E20" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G20" s="70" t="s">
+      <c r="G20" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="63" t="s">
         <v>165</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="58">
         <v>1100000</v>
       </c>
-      <c r="D21" s="67" t="s">
+      <c r="D21" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="75" t="s">
+      <c r="F21" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G21" s="70" t="s">
+      <c r="G21" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="58">
         <v>1004484</v>
       </c>
-      <c r="D22" s="67" t="s">
+      <c r="D22" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="73" t="s">
+      <c r="E22" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="G22" s="70" t="s">
+      <c r="G22" s="62" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="66">
+      <c r="C23" s="58">
         <v>1000000</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="D23" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E23" s="72" t="s">
+      <c r="E23" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="70" t="s">
+      <c r="G23" s="62" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="58">
         <v>840000</v>
       </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="69" t="s">
+      <c r="D24" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="70" t="s">
+      <c r="G24" s="62" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="67" t="s">
+      <c r="A25" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="66">
+      <c r="C25" s="58">
         <v>824838</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E25" s="72" t="s">
+      <c r="E25" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="70" t="s">
+      <c r="F25" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="70" t="s">
+      <c r="G25" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="66">
+      <c r="C26" s="58">
         <v>620035.83999999997</v>
       </c>
-      <c r="D26" s="67" t="s">
+      <c r="D26" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E26" s="69" t="s">
+      <c r="E26" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="75" t="s">
+      <c r="F26" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
+      <c r="A27" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="71" t="s">
+      <c r="B27" s="63" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="66">
+      <c r="C27" s="58">
         <v>274409.84999999998</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="D27" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="72" t="s">
+      <c r="E27" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="70" t="s">
+      <c r="G27" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="67" t="s">
+      <c r="A28" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="66">
+      <c r="C28" s="58">
         <v>250000</v>
       </c>
-      <c r="D28" s="67" t="s">
+      <c r="D28" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="73" t="s">
+      <c r="E28" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="76" t="s">
+      <c r="F28" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="G28" s="70" t="s">
+      <c r="G28" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="66">
+      <c r="C29" s="58">
         <v>167000</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E29" s="74" t="s">
+      <c r="E29" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="G29" s="70" t="s">
+      <c r="G29" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="67" t="s">
+      <c r="A30" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="63" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="66">
+      <c r="C30" s="58">
         <v>150000</v>
       </c>
-      <c r="D30" s="67" t="s">
+      <c r="D30" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="72" t="s">
+      <c r="E30" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="76" t="s">
+      <c r="F30" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="70" t="s">
+      <c r="G30" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="66">
+      <c r="C31" s="58">
         <v>128992.98</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="D31" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E31" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="F31" s="76" t="s">
+      <c r="F31" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="G31" s="70" t="s">
+      <c r="G31" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="67" t="s">
+      <c r="A32" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="C32" s="66">
+      <c r="C32" s="58">
         <v>120000</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="76" t="s">
+      <c r="F32" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="62" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="B33" s="71" t="s">
+      <c r="B33" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="C33" s="66">
+      <c r="C33" s="58">
         <v>100000</v>
       </c>
-      <c r="D33" s="67" t="s">
+      <c r="D33" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="72" t="s">
+      <c r="E33" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="76" t="s">
+      <c r="F33" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="G33" s="70" t="s">
+      <c r="G33" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="77" t="s">
+      <c r="A34" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="79" t="s">
+      <c r="B34" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="70">
         <v>35000</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="D34" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="E34" s="80" t="s">
+      <c r="E34" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="70" t="s">
+      <c r="F34" s="62" t="s">
         <v>176</v>
       </c>
-      <c r="G34" s="70" t="s">
+      <c r="G34" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="79" t="s">
+      <c r="B35" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="C35" s="78">
+      <c r="C35" s="70">
         <v>30600</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="D35" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="81" t="s">
+      <c r="E35" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="F35" s="82" t="s">
+      <c r="F35" s="74" t="s">
         <v>178</v>
       </c>
-      <c r="G35" s="70" t="s">
+      <c r="G35" s="62" t="s">
         <v>141</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A1:E1"/>
@@ -3234,7 +3237,6 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E17:E35" xr:uid="{2EF9A1E0-747A-43D2-B879-3D0774406198}">
@@ -3256,17 +3258,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
     </row>
@@ -3297,17 +3299,17 @@
       <c r="K3" s="18"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
     </row>
@@ -3364,16 +3366,16 @@
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
@@ -3557,11 +3559,11 @@
       <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="84"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
     </row>

--- a/Friopacking_Objetivos_2_3_4_5.xlsx
+++ b/Friopacking_Objetivos_2_3_4_5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrodriguez\Desktop\Directorio J\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F73501-D9AD-4B24-B256-BB9EA1D7D8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FE3697-D471-4459-B6EA-9C4E00C4019C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetivo 2" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="164">
   <si>
     <t>OBJETIVO 2 — EJECUTAR PROYECTOS CON REFRIGERANTE CO2</t>
   </si>
@@ -116,18 +116,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t>HUGO ESCOBAR</t>
-  </si>
-  <si>
-    <t>AXION LOG</t>
-  </si>
-  <si>
-    <t>CD TRUJILLO</t>
-  </si>
-  <si>
-    <t>Prospecto</t>
-  </si>
-  <si>
     <t>Clientes únicos vendidos marcados como 'nuevo fuera de Agro' — meta 4 clientes</t>
   </si>
   <si>
@@ -359,25 +347,10 @@
     <t>Zedina</t>
   </si>
   <si>
-    <t>Jesus Chavez</t>
-  </si>
-  <si>
     <t>NGR - NUTRA</t>
   </si>
   <si>
     <t>Perupez</t>
-  </si>
-  <si>
-    <t>Talma</t>
-  </si>
-  <si>
-    <t>Cementos Pacasmayo</t>
-  </si>
-  <si>
-    <t>Instalacion de 2 Chilleres - Ecuador</t>
-  </si>
-  <si>
-    <t>Europan - San Antonio</t>
   </si>
   <si>
     <t>PIPELINE</t>
@@ -456,12 +429,6 @@
     <t>% PROBABILIDAD DE ÉXITO</t>
   </si>
   <si>
-    <t>YAMBOLI</t>
-  </si>
-  <si>
-    <t>Camaras de congelado de helado (sistema de frio) : C02 y Freon</t>
-  </si>
-  <si>
     <t>En proceso de cotización</t>
   </si>
   <si>
@@ -471,12 +438,6 @@
     <t>CO2</t>
   </si>
   <si>
-    <t>Broom Frio</t>
-  </si>
-  <si>
-    <t>3 Camaras y pasillo de despacho</t>
-  </si>
-  <si>
     <t>Norte</t>
   </si>
   <si>
@@ -519,18 +480,9 @@
     <t>NO AGRO</t>
   </si>
   <si>
-    <t>Jose Perez</t>
-  </si>
-  <si>
     <t>INFRAESTRUCTURA</t>
   </si>
   <si>
-    <t>RANSA</t>
-  </si>
-  <si>
-    <t>planta de congelado - callao ó Paita</t>
-  </si>
-  <si>
     <t>NH3</t>
   </si>
   <si>
@@ -538,49 +490,49 @@
   </si>
   <si>
     <t>implementación de cámaras de frio para Planta de producción Proyecto Chronos (freon)</t>
-  </si>
-  <si>
-    <t>Pesquera Altair-Oceano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camara de congelado y Anden de congelado </t>
   </si>
   <si>
     <t xml:space="preserve">PRODUCTOS NATURALES DE EXPORTACION S.A. - PRONEX S.A.
 </t>
   </si>
   <si>
-    <t>Planta de carnicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cámaras de refrigeracion y congelados </t>
-  </si>
-  <si>
     <t>Hayduk</t>
   </si>
   <si>
-    <t>Lineas de proceso de agua helada y agua de torre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molitalia </t>
-  </si>
-  <si>
-    <t>Suministro de Chiller</t>
-  </si>
-  <si>
-    <t>Ingeneria</t>
-  </si>
-  <si>
-    <t>Servicio Ingeniería</t>
-  </si>
-  <si>
-    <t>Expediente técnico</t>
-  </si>
-  <si>
-    <t>Servicio Arquitectura</t>
-  </si>
-  <si>
     <t>Perú</t>
+  </si>
+  <si>
+    <t>Greenfield ECLA Amoniaco/Glicol (Sistema de Frio)</t>
+  </si>
+  <si>
+    <t>Agro Fruit Export SAC</t>
+  </si>
+  <si>
+    <t>Cámara de congelado</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>centro</t>
+  </si>
+  <si>
+    <t>norte</t>
+  </si>
+  <si>
+    <t>Cámara de congelado 180 posiciones</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>Cámara y antecámara de yogurt</t>
+  </si>
+  <si>
+    <t>Freón</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -594,7 +546,7 @@
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,18 +666,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -745,13 +685,8 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,12 +767,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -855,7 +784,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -932,36 +861,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right style="thin">
-        <color theme="4"/>
-      </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -973,15 +872,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1059,14 +949,25 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="4"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1101,9 +1002,6 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1203,108 +1101,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1319,10 +1151,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1337,19 +1169,86 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1618,289 +1517,263 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" style="17" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
     </row>
     <row r="9" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="D10" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="E10" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="72" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="B11" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="C11" s="73">
+        <v>856138</v>
+      </c>
+      <c r="D11" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="71">
+        <v>20</v>
+      </c>
+      <c r="H11" s="71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A12" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="B12" s="71" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="73">
+        <v>824838</v>
+      </c>
+      <c r="D12" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="E12" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="71">
+        <v>40</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A13" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="H10" s="43" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="46">
-        <v>3500000</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="45">
+      <c r="C13" s="73">
+        <v>167000</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="71">
+        <v>80</v>
+      </c>
+      <c r="H13" s="71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A14" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="73">
+        <v>2096567.37</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="71">
+        <v>60</v>
+      </c>
+      <c r="H14" s="71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A15" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="73">
+        <v>1500000</v>
+      </c>
+      <c r="D15" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="71">
         <v>20</v>
       </c>
-      <c r="H11" s="45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="46">
-        <v>2850000</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G12" s="45">
-        <v>40</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="46">
-        <v>1004484</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G13" s="45">
-        <v>5</v>
-      </c>
-      <c r="H13" s="45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="46">
-        <v>1000000</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="45">
-        <v>20</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="46">
-        <v>824838</v>
-      </c>
-      <c r="D15" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G15" s="45">
-        <v>60</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="46">
-        <v>167000</v>
-      </c>
-      <c r="D16" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G16" s="45">
-        <v>80</v>
-      </c>
-      <c r="H16" s="45" t="s">
-        <v>115</v>
+      <c r="H15" s="71" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1914,7 +1787,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D11:D16" xr:uid="{75AE35ED-7284-4EE0-92EA-54FA47207936}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D11:D15" xr:uid="{75AE35ED-7284-4EE0-92EA-54FA47207936}">
       <formula1>"Negociación,En análisis del cliente,En proceso de cotización,Vendido,Perdido,Postpuesto,Prospecto,Cancelado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1925,7 +1798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1939,158 +1812,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="A1" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
+      <c r="B4" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
+      <c r="B5" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="85" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="B6" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+        <v>47</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
+        <v>49</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="85" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+      <c r="B9" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -2101,7 +1974,7 @@
     </row>
     <row r="14" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B14" s="8">
         <v>2691054.14</v>
@@ -2118,7 +1991,7 @@
     </row>
     <row r="15" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15" s="8">
         <v>2735162.48</v>
@@ -2135,7 +2008,7 @@
     </row>
     <row r="16" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B16" s="8">
         <v>5426216.6200000001</v>
@@ -2144,15 +2017,15 @@
         <v>2800000</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B17" s="8">
         <v>0</v>
@@ -2169,7 +2042,7 @@
     </row>
     <row r="18" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B18" s="8">
         <v>647109.29</v>
@@ -2186,7 +2059,7 @@
     </row>
     <row r="19" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B19" s="8">
         <v>8</v>
@@ -2202,17 +2075,17 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="87"/>
+      <c r="A21" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -2228,30 +2101,30 @@
         <v>21</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D23" s="8">
         <v>9500000</v>
@@ -2262,10 +2135,10 @@
       <c r="F23" s="8">
         <v>2475725</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="11">
         <v>4746468</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <v>0.18</v>
       </c>
       <c r="I23" s="4">
@@ -2274,13 +2147,13 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D24" s="8">
         <v>718498.3</v>
@@ -2291,10 +2164,10 @@
       <c r="F24" s="8">
         <v>26235.1</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>126074.7</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="9">
         <v>0.19</v>
       </c>
       <c r="I24" s="4">
@@ -2303,13 +2176,13 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D25" s="8">
         <v>552380.14</v>
@@ -2320,10 +2193,10 @@
       <c r="F25" s="8">
         <v>50836.31</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>166270.25</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="9">
         <v>0.15</v>
       </c>
       <c r="I25" s="4">
@@ -2332,13 +2205,13 @@
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D26" s="8">
         <v>379901.83</v>
@@ -2349,10 +2222,10 @@
       <c r="F26" s="8">
         <v>84519.33</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>189666.94</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="9">
         <v>0.18</v>
       </c>
       <c r="I26" s="4">
@@ -2361,13 +2234,13 @@
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D27" s="8">
         <v>110710</v>
@@ -2378,10 +2251,10 @@
       <c r="F27" s="8">
         <v>0</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="11">
         <v>10710</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="9">
         <v>0.14000000000000001</v>
       </c>
       <c r="I27" s="4">
@@ -2390,13 +2263,13 @@
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D28" s="8">
         <v>97846.74</v>
@@ -2407,10 +2280,10 @@
       <c r="F28" s="8">
         <v>97846.74</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>97846.74</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <v>0.15</v>
       </c>
       <c r="I28" s="4">
@@ -2419,13 +2292,13 @@
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D29" s="8">
         <v>50864.99</v>
@@ -2436,10 +2309,10 @@
       <c r="F29" s="8">
         <v>0</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>50864.99</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <v>0.15</v>
       </c>
       <c r="I29" s="4">
@@ -2448,13 +2321,13 @@
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D30" s="8">
         <v>38315</v>
@@ -2465,10 +2338,10 @@
       <c r="F30" s="8">
         <v>0</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>38315</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>0.15</v>
       </c>
       <c r="I30" s="4">
@@ -2476,119 +2349,110 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="88"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="88"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A32" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="E33" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="8">
+    <row r="34" spans="1:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="78">
         <v>567000</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="78">
         <v>0</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="78">
         <v>29663</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="9">
+      <c r="G34" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="79">
         <v>0.6</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="54" x14ac:dyDescent="0.3">
-      <c r="A36" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="46">
+      <c r="I34" s="77" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+      <c r="A35" s="50"/>
+      <c r="B35" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="73">
         <v>3000000</v>
       </c>
-      <c r="D36" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="G36" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="J36" s="45">
-        <v>60</v>
-      </c>
-      <c r="K36" s="45">
-        <v>10</v>
-      </c>
-      <c r="L36" s="48">
-        <v>7</v>
-      </c>
-      <c r="M36" s="78">
-        <v>2026</v>
+      <c r="E35" s="78">
+        <v>0</v>
+      </c>
+      <c r="F35" s="73">
+        <v>3000000</v>
+      </c>
+      <c r="G35" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="79">
+        <v>0.6</v>
+      </c>
+      <c r="I35" s="80" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B6:I6"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="B7:I7"/>
@@ -2596,20 +2460,7 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B6:I6"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I36" xr:uid="{1D3A478F-344B-4E54-B296-768D75F24C9F}">
-      <formula1>"Paolo Villa,Manuel Henriquez,Sebastian Flores,Jose Perez,Jhon Rojas,Jesus,Elver Leon,Hugo,Arquitectura,Pablo Y"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D36" xr:uid="{7C45FF86-D851-4A7C-8367-9E3C21F8153B}">
-      <formula1>"Negociación,En análisis del cliente,En proceso de cotización,Vendido,Perdido,Postpuesto,Prospecto,Cancelado"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2617,615 +2468,434 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" style="38" customWidth="1"/>
-    <col min="2" max="2" width="42" style="21" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="28" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="21" customWidth="1"/>
+    <col min="1" max="1" width="28" style="37" customWidth="1"/>
+    <col min="2" max="2" width="42" style="20" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="28" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="3" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+    </row>
+    <row r="6" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+    </row>
+    <row r="9" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="70"/>
+    </row>
+    <row r="10" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="25">
+        <v>203678.39</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="25">
+        <v>25500</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.23</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="25">
+        <v>17083.21</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="47">
+        <v>3000000</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="47">
+        <v>1258345.392</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-    </row>
-    <row r="3" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-    </row>
-    <row r="4" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-    </row>
-    <row r="5" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-    </row>
-    <row r="6" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-    </row>
-    <row r="7" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-    </row>
-    <row r="9" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="89" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="90"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="91"/>
-    </row>
-    <row r="10" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="22" t="s">
+      <c r="F18" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="47">
+        <v>935527.66</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="47">
+        <v>1000000</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="48" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="26">
-        <v>203678.39</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="B21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="47">
+        <v>824838</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="47">
+        <v>620035.83999999997</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="47">
+        <v>0</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="47">
+        <v>167000</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="26">
-        <v>25500</v>
-      </c>
-      <c r="D12" s="16">
-        <v>0.23</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="26">
-        <v>17083.21</v>
-      </c>
-      <c r="D13" s="16">
-        <v>0.13</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="92" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-    </row>
-    <row r="16" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="54" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="F16" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="58">
-        <v>3500000</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="61" t="s">
+      <c r="F24" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="G17" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="63" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="58">
-        <v>3000000</v>
-      </c>
-      <c r="D18" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="62" t="s">
+      <c r="C25" s="83">
+        <v>300000</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="86" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="90" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="91">
+        <v>2096567.37</v>
+      </c>
+      <c r="D26" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="86" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="86" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="87" t="s">
         <v>160</v>
       </c>
-      <c r="G18" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="B27" s="88" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="C27" s="89">
+        <v>365000</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="93" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="58">
-        <v>1950000</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E19" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="62" t="s">
+      <c r="G27" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="58">
-        <v>1572931.74</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" s="58">
-        <v>1100000</v>
-      </c>
-      <c r="D21" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E21" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="G21" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="58">
-        <v>1004484</v>
-      </c>
-      <c r="D22" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="68" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="63" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="58">
-        <v>1000000</v>
-      </c>
-      <c r="D23" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="B24" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" s="58">
-        <v>840000</v>
-      </c>
-      <c r="D24" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="58">
-        <v>824838</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E25" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="58">
-        <v>620035.83999999997</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="G26" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="58">
-        <v>274409.84999999998</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F27" s="62" t="s">
-        <v>164</v>
-      </c>
-      <c r="G27" s="62" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="28" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="58">
-        <v>250000</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="B29" s="63" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="58">
-        <v>167000</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="G29" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="63" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30" s="58">
-        <v>150000</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="G30" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="58">
-        <v>128992.98</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="G31" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="B32" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="58">
-        <v>120000</v>
-      </c>
-      <c r="D32" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" s="62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="59" t="s">
-        <v>173</v>
-      </c>
-      <c r="B33" s="63" t="s">
-        <v>174</v>
-      </c>
-      <c r="C33" s="58">
-        <v>100000</v>
-      </c>
-      <c r="D33" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="F33" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="G33" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C34" s="70">
-        <v>35000</v>
-      </c>
-      <c r="D34" s="69" t="s">
-        <v>158</v>
-      </c>
-      <c r="E34" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="G34" s="62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="C35" s="70">
-        <v>30600</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>158</v>
-      </c>
-      <c r="E35" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G35" s="62" t="s">
-        <v>141</v>
-      </c>
+      <c r="E28" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3239,12 +2909,12 @@
     <mergeCell ref="A6:E6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E17:E35" xr:uid="{2EF9A1E0-747A-43D2-B879-3D0774406198}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E17:E27" xr:uid="{2EF9A1E0-747A-43D2-B879-3D0774406198}">
       <formula1>"Negociación,En análisis del cliente,En proceso de cotización,Vendido,Perdido,Postpuesto,Prospecto,Cancelado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3258,60 +2928,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="A1" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -3320,300 +2990,300 @@
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
-        <v>92</v>
+      <c r="A6" s="31" t="s">
+        <v>88</v>
       </c>
       <c r="B6" s="6">
         <f>C14</f>
         <v>330083.68</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>250000</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="25">
+        <v>87009.29</v>
+      </c>
+      <c r="D10" s="15">
+        <v>0.22</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="25">
+        <v>24240</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="25">
+        <v>203678.39</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="C13" s="25">
+        <v>15156</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.27</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="26">
-        <v>87009.29</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0.22</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="G13" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="26">
-        <v>24240</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="26">
-        <v>203678.39</v>
-      </c>
-      <c r="D12" s="16">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="26">
-        <v>15156</v>
-      </c>
-      <c r="D13" s="16">
-        <v>0.27</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="40">
+      <c r="C14" s="39">
         <f>SUM(C10:C13)</f>
         <v>330083.68</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="30"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="29"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="30"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="29"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="83" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
+      <c r="A16" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="A17" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="26">
+      <c r="A18" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="25">
         <v>60000</v>
       </c>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="36">
+      <c r="A19" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="35">
         <v>22000</v>
       </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="36">
+      <c r="A20" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="35">
         <v>167000</v>
       </c>
     </row>
